--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -1674,7 +1674,7 @@
       <c r="C41" s="12" t="inlineStr"/>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Open, Decided, Withdrawn</t>
+          <t>Open, Configurable – BDOI to confirm the setting, Decided, Withdrawn</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Issue at save for counter, file and PDC payments, so the client gets the AR at once and the series is used in order; give the TL a daily review list. If BDOI keeps the posting step, make it a configurable approval per receipt type (for example manual ORs only). (the system reference FRS: “Issue AR and Apply” issues the AR from the branch series, applies the payment and opens the receipt (FR-OP-011); ORs likewise (FR-OP-012).)</t>
+          <t>Issue at save for counter, file and PDC payments, so the client gets the AR at once and the series is used in order; give the TL a daily review list. If BDOI keeps the posting step, make it a configurable approval per receipt type (for example manual ORs only). (the system reference FRS: “Issue AR and Apply” issues the AR from the branch series, applies the payment and opens the receipt (FR-OP-011); ORs likewise (FR-OP-012).) Available as a setting: Setting of the receipts that need the posting step: AR and OR (BDOI's reading) by default; blank issues the number at save.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -4195,7 +4195,7 @@
       <c r="I5" s="12" t="inlineStr"/>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Both, under one Reinstate action with the BRD's reasons: “Due to Cancellation” and bounced check restore a cancelled receipt; mis-application and withholding tax adjustment reverse the application of an issued receipt for re-application. (the system reference FRS: Reinstate a cancelled receipt in full or in part; the reinstated amount is applied to the encoded invoice (FR-OP-014). Reversal of an issued receipt's application is the payment reversal of Incoming Requests.)</t>
+          <t>Both, under one Reinstate action with the BRD's reasons: “Due to Cancellation” and bounced check restore a cancelled receipt; mis-application and withholding tax adjustment reverse the application of an issued receipt for re-application. (the system reference FRS: Reinstate a cancelled receipt in full or in part; the reinstated amount is applied to the encoded invoice (FR-OP-014). Reversal of an issued receipt's application is the payment reversal of Incoming Requests.) Available as a setting: Setting of what Reinstate does: issued receipts (BDOI's reading), cancelled receipts, or both (by default).</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -4231,7 +4231,7 @@
       <c r="I6" s="12" t="inlineStr"/>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's prefixes with the year (for example CN-AR-2026-000001); the numbering is configuration. (the system reference FRS: Cancellation CAN-yyyy-n and reinstatement RIN-yyyy-n (FR-OP-013, 014).)</t>
+          <t>Adopt BDOI's prefixes with the year (for example CN-AR-2026-000001); the numbering is configuration. (the system reference FRS: Cancellation CAN-yyyy-n and reinstatement RIN-yyyy-n (FR-OP-013, 014).) Available as a setting: Setting of the record number format: prefix, type and sequence by default.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -4267,7 +4267,7 @@
       <c r="I7" s="12" t="inlineStr"/>
       <c r="J7" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Keep 10.00 as in the BRD unless BDOI decides otherwise; it is a parameter. (the system reference FRS: Default 10.00 for premium and excess, configurable (FR-OP-023).)</t>
+          <t>Keep 10.00 as in the BRD unless BDOI decides otherwise; it is a parameter. (the system reference FRS: Default 10.00 for premium and excess, configurable (FR-OP-023).) Available as a setting: Setting of the minimal balance threshold: 10.00 by default (BRD).</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -4303,7 +4303,7 @@
       <c r="I8" s="12" t="inlineStr"/>
       <c r="J8" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Keep FST as its own component after LGT (it is booked on fire policies); apply check payments before cash payments on the same invoice on the same day. (the system reference FRS: DST, VAT, LGT, FST, other charges, basic premium; check before cash open (FR-OP-019, OQ09).)</t>
+          <t>Keep FST as its own component after LGT (it is booked on fire policies); apply check payments before cash payments on the same invoice on the same day. (the system reference FRS: DST, VAT, LGT, FST, other charges, basic premium; check before cash open (FR-OP-019, OQ09).) Available as a setting: Setting of the order of the payments of one posting run: checks before cash by default.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -4339,7 +4339,7 @@
       <c r="I9" s="12" t="inlineStr"/>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Accept the check when it is presented (a post-dated check goes to the PDC warehouse); keep the holding period for remittance only. (the system reference FRS: No check-date validation at receipt; 3 banking days before the payment is remitted (FR-OP-031, RMTID.017).)</t>
+          <t>Accept the check when it is presented (a post-dated check goes to the PDC warehouse); keep the holding period for remittance only. (the system reference FRS: No check-date validation at receipt; 3 banking days before the payment is remitted (FR-OP-031, RMTID.017).) Available as a setting: Settings of the check date rule (on) and of the holding period (4 working days).</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -4375,7 +4375,7 @@
       <c r="I10" s="12" t="inlineStr"/>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's reading: the file identifies unmatched payments already receipted, so no second AR; new money arrives through the other channels. (the system reference FRS: Every Direct Credit row is a new payment with its own AR (FR-OP-015).)</t>
+          <t>Adopt BDOI's reading: the file identifies unmatched payments already receipted, so no second AR; new money arrives through the other channels. (the system reference FRS: Every Direct Credit row is a new payment with its own AR (FR-OP-015).) Available as a setting: Setting of the reading of the Direct Credit file: identification of payments already received (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -4411,7 +4411,7 @@
       <c r="I11" s="12" t="inlineStr"/>
       <c r="J11" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's rule; it matches how our Adjustment FRs handle remitted premium (AR Insurer, FR-OP-057). (the system reference FRS: Every application is reversed and the invoices are outstanding again (FR-OP-013).)</t>
+          <t>Adopt BDOI's rule; it matches how our Adjustment FRs handle remitted premium (AR Insurer, FR-OP-057). (the system reference FRS: Every application is reversed and the invoices are outstanding again (FR-OP-013).) Available as a setting: Setting of the cancellation of a remitted AR: AR insurer refund (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -4447,7 +4447,7 @@
       <c r="I12" s="12" t="inlineStr"/>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Line-level processing as BRQID.006 asks, with the exceptions listed; partial payments allowed and shown as such. (the system reference FRS: Valid lines are staged and issued; failed lines stay staged with their reason (FR-OP-021).)</t>
+          <t>Line-level processing as BRQID.006 asks, with the exceptions listed; partial payments allowed and shown as such. (the system reference FRS: Valid lines are staged and issued; failed lines stay staged with their reason (FR-OP-021).) Available as a setting: Setting of the commission schedule with failed or unmatched lines: valid lines processed (BRD) by default; whole file refused available.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -4483,7 +4483,7 @@
       <c r="I13" s="12" t="inlineStr"/>
       <c r="J13" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership decides the point at which the commission OR is issued; moving it to the Disbursement approval is a change to the system. (the system reference FRS: The commission OR is issued when the Remittance TL approves the batch (FR-OP-035).)</t>
+          <t>Comptrollership decides the point at which the commission OR is issued; moving it to the Disbursement approval is a change to the system. (the system reference FRS: The commission OR is issued when the Remittance TL approves the batch (FR-OP-035).) Available as a setting: Setting of the point the settlement OR is issued: at the approval of Disbursement (BDOI's reading) by default; at the remittance approval available.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -4555,7 +4555,7 @@
       <c r="I15" s="12" t="inlineStr"/>
       <c r="J15" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Keep Cashiering ownership with requests from Collections, as the BRD-4 Collections FRS specifies; give Marketing read access to the items of its unit. (the system reference FRS: The Cashier assigns and the Cashiering TL approves; Collections asks through Incoming Requests (FR-OP-022; BRD-4).)</t>
+          <t>Keep Cashiering ownership with requests from Collections, as the BRD-4 Collections FRS specifies; give Marketing read access to the items of its unit. (the system reference FRS: The Cashier assigns and the Cashiering TL approves; Collections asks through Incoming Requests (FR-OP-022; BRD-4).) Available as a setting: Setting of what Marketing users see in the unapplied payment list: their marketing unit (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -4591,7 +4591,7 @@
       <c r="I16" s="12" t="inlineStr"/>
       <c r="J16" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Set 50 MB. (the system reference FRS: Not stated; the system accepts files up to 25 MB.)</t>
+          <t>Set 50 MB. (the system reference FRS: Not stated; the system accepts files up to 25 MB.) Available as a setting: Size limit per payment file type: 50 MB by default.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -4735,7 +4735,7 @@
       <c r="I20" s="12" t="inlineStr"/>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Keep the BRD list (it is a maintained list); add the check-payment restriction if BDOI wants it. (the system reference FRS: The BRD lists in four groups, including Check not picked-up, Negative VAT, Discount not applied, PDC retrieval / replacement, Bounced or returned check, Error printing.)</t>
+          <t>Keep the BRD list (it is a maintained list); add the check-payment restriction if BDOI wants it. (the system reference FRS: The BRD lists in four groups, including Check not picked-up, Negative VAT, Discount not applied, PDC retrieval / replacement, Bounced or returned check, Error printing.) Available as a setting: List of the cancellation reasons allowed for a check payment, by default.</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="I22" s="12" t="inlineStr"/>
       <c r="J22" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enforce it through BDO's network and device policy if required; no change to the screens. (the system reference FRS: Log-in from a browser; responsive screens.)</t>
+          <t>Enforce it through BDO's network and device policy if required; no change to the screens. (the system reference FRS: Log-in from a browser; responsive screens.) Available as a setting: Setting of the device restriction: off by default for SIT; on with the company networks and the device header of BDOI IT.</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="I25" s="12" t="inlineStr"/>
       <c r="J25" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Bank account mandatory (defaulted by currency as BDOI proposes); remarks optional. (the system reference FRS: Neither field exists on Receive Payment.)</t>
+          <t>Bank account mandatory (defaulted by currency as BDOI proposes); remarks optional. (the system reference FRS: Neither field exists on Receive Payment.) Available as a setting: Setting of the remarks of an AR: mandatory by default.</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -4951,7 +4951,7 @@
       <c r="I26" s="12" t="inlineStr"/>
       <c r="J26" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Tag per account, defaulted from the client; Comptrollership states the base of the 2% (basic or gross premium); the system keeps the share applied as a parameter. (the system reference FRS: 2% CWT client flag; 98% of the premium applied (FR-OP-018; OQ10).)</t>
+          <t>Tag per account, defaulted from the client; Comptrollership states the base of the 2% (basic or gross premium); the system keeps the share applied as a parameter. (the system reference FRS: 2% CWT client flag; 98% of the premium applied (FR-OP-018; OQ10).) Available as a setting: Setting of the base of the PR 2307: the premium amount by default; the basic premium available.</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -4987,7 +4987,7 @@
       <c r="I27" s="12" t="inlineStr"/>
       <c r="J27" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>BDOI to give one format per receipt kind; the system sets it as the series prefix and range without a change.</t>
+          <t>BDOI to give one format per receipt kind; the system sets it as the series prefix and range without a change. Available as a setting: Settings of the AR and OR number format (prefix, year, branch indicator, sequence) and of the certificate number (AC, branch, month and year, sequence).</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -5095,7 +5095,7 @@
       <c r="I30" s="12" t="inlineStr"/>
       <c r="J30" s="25" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="J5:J587" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
-      <formula1>'Lists'!$D$2:$D$4</formula1>
+      <formula1>'Lists'!$D$2:$D$5</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -7197,7 +7197,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D3" s="34" t="inlineStr">
         <is>
-          <t>Decided</t>
+          <t>Configurable – BDOI to confirm the setting</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Decided</t>
         </is>
       </c>
     </row>
@@ -7297,6 +7297,11 @@
       <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Approved</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.02.01.02-AC01, TC-FRS-CSH.02.01.02-AC02, TC-FRS-CSH.02.01.02-AC03, TC-FRS-CSH.02.01.02-AC04, TC-OP-011.1-01</t>
+          <t>TC-FRS-CSH.02.01.02-AC01, TC-FRS-CSH.02.01.02-AC02, TC-FRS-CSH.02.01.02-AC03, TC-FRS-CSH.02.01.02-AC04, TC-OP-011.4-01</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>TC-OP-015.1-01, TC-OP-015.2-01, TC-OP-015.3-01, TC-OP-015.3-02</t>
+          <t>TC-OP-015.4-01, TC-OP-015.4-02, TC-OP-015.1-01, TC-OP-015.2-01, TC-OP-015.3-01</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.07.01.01-AC01, TC-OP-021.1-01, TC-OP-021.1-02, TC-OP-021.2-01, TC-OP-021.2-02</t>
+          <t>TC-FRS-CSH.07.01.01-AC01, TC-OP-021.3-01, TC-OP-021.1-01, TC-OP-021.1-02, TC-OP-021.2-01</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.05.01.04-AC01, TC-FRS-CSH.05.01.04-AC02, TC-OP-015.1-01, TC-OP-015.2-01, TC-OP-015.3-01</t>
+          <t>TC-FRS-CSH.05.01.04-AC01, TC-FRS-CSH.05.01.04-AC02, TC-OP-015.4-01, TC-OP-015.4-02, TC-OP-015.1-01</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.02.04.07-AC01, TC-OP-025.1-01, TC-OP-025.2-01, TC-OP-025.2-02</t>
+          <t>TC-FRS-CSH.02.04.07-AC01, TC-OP-025.3-01, TC-OP-025.3-02, TC-OP-025.1-01, TC-OP-025.2-01</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.02.06.01-AC01, TC-OP-025.1-01, TC-OP-025.2-01, TC-OP-025.2-02, TC-FRS-CSH.02.06.02-AC01</t>
+          <t>TC-FRS-CSH.02.06.01-AC01, TC-OP-025.3-01, TC-OP-025.3-02, TC-OP-025.1-01, TC-OP-025.2-01</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.01.03.02-AC01, TC-FRS-CSH.01.03.02-AC02, TC-FRS-CSH.01.03.02-AC03, TC-OP-003.1-01, TC-OP-003.2-01</t>
+          <t>TC-FRS-CSH.01.03.02-AC01, TC-FRS-CSH.01.03.02-AC02, TC-FRS-CSH.01.03.02-AC03, TC-OP-003.4-01, TC-OP-003.1-01</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.02.04.07-AC01, TC-OP-025.1-01, TC-OP-025.2-01, TC-OP-025.2-02</t>
+          <t>TC-FRS-CSH.02.04.07-AC01, TC-OP-025.3-01, TC-OP-025.3-02, TC-OP-025.1-01, TC-OP-025.2-01</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.02.01.16-AC01, TC-OP-011.1-01, TC-OP-011.2-01, TC-OP-011.2-02, TC-OP-011.3-01</t>
+          <t>TC-FRS-CSH.02.01.16-AC01, TC-OP-011.4-01, TC-OP-011.4-02, TC-OP-011.4-03, TC-OP-011.4-04</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       <c r="S20" s="12" t="inlineStr"/>
       <c r="T20" s="12" t="inlineStr">
         <is>
-          <t>TC-FRS-CSH.06.02.02-AC01, TC-FRS-CSH.06.02.02-AC02, TC-OP-022.1-01, TC-OP-022.2-01, TC-OP-022.2-02</t>
+          <t>TC-FRS-CSH.06.02.02-AC01, TC-FRS-CSH.06.02.02-AC02, TC-OP-022.4-01, TC-OP-022.1-01, TC-OP-022.2-01</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Issue at save for counter, file and PDC payments, so the client gets the AR at once and the series is used in order; give the TL a daily review list. If BDOI keeps the posting step, make it a configurable approval per receipt type (for example manual ORs only). (the system reference FRS: “Issue AR and Apply” issues the AR from the branch series, applies the payment and opens the receipt (FR-OP-011); ORs likewise (FR-OP-012).) Available as a setting: Setting of the receipts that need the posting step: AR and OR (BDOI's reading) by default; blank issues the number at save.</t>
+          <t>Issue at save for counter, file and PDC payments, so the client gets the AR at once and the series is used in order; give the TL a daily review list. If BDOI keeps the posting step, make it a configurable approval per receipt type (for example manual ORs only). Proposed behaviour: “Issue AR and Apply” issues the AR from the branch series, applies the payment and opens the receipt; ORs likewise. Available as a setting: Setting of the receipts that need the posting step: AR and OR (BDOI's reading) by default; blank issues the number at save.</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Both, under one Reinstate action with the BRD's reasons: “Due to Cancellation” and bounced check restore a cancelled receipt; mis-application and withholding tax adjustment reverse the application of an issued receipt for re-application. (the system reference FRS: Reinstate a cancelled receipt in full or in part; the reinstated amount is applied to the encoded invoice (FR-OP-014). Reversal of an issued receipt's application is the payment reversal of Incoming Requests.) Available as a setting: Setting of what Reinstate does: issued receipts (BDOI's reading), cancelled receipts, or both (by default).</t>
+          <t>Both, under one Reinstate action with the BRD's reasons: “Due to Cancellation” and bounced check restore a cancelled receipt; mis-application and withholding tax adjustment reverse the application of an issued receipt for re-application. Proposed behaviour: Reinstate a cancelled receipt in full or in part; the reinstated amount is applied to the encoded invoice. Reversal of an issued receipt's application is the payment reversal of Incoming Requests. Available as a setting: Setting of what Reinstate does: issued receipts (BDOI's reading), cancelled receipts, or both (by default).</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's prefixes with the year (for example CN-AR-2026-000001); the numbering is configuration. (the system reference FRS: Cancellation CAN-yyyy-n and reinstatement RIN-yyyy-n (FR-OP-013, 014).) Available as a setting: Setting of the record number format: prefix, type and sequence by default.</t>
+          <t>Adopt BDOI's prefixes with the year (for example CN-AR-2026-000001); the numbering is configuration. Proposed behaviour: Cancellation CAN-yyyy-n and reinstatement RIN-yyyy-n (014). Available as a setting: Setting of the record number format: prefix, type and sequence by default.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Keep 10.00 as in the BRD unless BDOI decides otherwise; it is a parameter. (the system reference FRS: Default 10.00 for premium and excess, configurable (FR-OP-023).) Available as a setting: Setting of the minimal balance threshold: 10.00 by default (BRD).</t>
+          <t>Keep 10.00 as in the BRD unless BDOI decides otherwise; it is a parameter. Proposed behaviour: Default 10.00 for premium and excess, configurable. Available as a setting: Setting of the minimal balance threshold: 10.00 by default (BRD).</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Keep FST as its own component after LGT (it is booked on fire policies); apply check payments before cash payments on the same invoice on the same day. (the system reference FRS: DST, VAT, LGT, FST, other charges, basic premium; check before cash open (FR-OP-019, OQ09).) Available as a setting: Setting of the order of the payments of one posting run: checks before cash by default.</t>
+          <t>Keep FST as its own component after LGT (it is booked on fire policies); apply check payments before cash payments on the same invoice on the same day. Proposed behaviour: DST, VAT, LGT, FST, other charges, basic premium; check before cash open. Available as a setting: Setting of the order of the payments of one posting run: checks before cash by default.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Accept the check when it is presented (a post-dated check goes to the PDC warehouse); keep the holding period for remittance only. (the system reference FRS: No check-date validation at receipt; 3 banking days before the payment is remitted (FR-OP-031, RMTID.017).) Available as a setting: Settings of the check date rule (on) and of the holding period (4 working days).</t>
+          <t>Accept the check when it is presented (a post-dated check goes to the PDC warehouse); keep the holding period for remittance only. Proposed behaviour: No check-date validation at receipt; 3 banking days before the payment is remitted (RMTID.017). Available as a setting: Settings of the check date rule (on) and of the holding period (4 working days).</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's reading: the file identifies unmatched payments already receipted, so no second AR; new money arrives through the other channels. (the system reference FRS: Every Direct Credit row is a new payment with its own AR (FR-OP-015).) Available as a setting: Setting of the reading of the Direct Credit file: identification of payments already received (BDOI's reading) by default.</t>
+          <t>Adopt BDOI's reading: the file identifies unmatched payments already receipted, so no second AR; new money arrives through the other channels. Proposed behaviour: Every Direct Credit row is a new payment with its own AR. Available as a setting: Setting of the reading of the Direct Credit file: identification of payments already received (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's rule; it matches how our Adjustment FRs handle remitted premium (AR Insurer, FR-OP-057). (the system reference FRS: Every application is reversed and the invoices are outstanding again (FR-OP-013).) Available as a setting: Setting of the cancellation of a remitted AR: AR insurer refund (BDOI's reading) by default.</t>
+          <t>Adopt BDOI's rule; it matches how our Adjustment FRs handle remitted premium (AR Insurer). Proposed behaviour: Every application is reversed and the invoices are outstanding again. Available as a setting: Setting of the cancellation of a remitted AR: AR insurer refund (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Line-level processing as BRQID.006 asks, with the exceptions listed; partial payments allowed and shown as such. (the system reference FRS: Valid lines are staged and issued; failed lines stay staged with their reason (FR-OP-021).) Available as a setting: Setting of the commission schedule with failed or unmatched lines: valid lines processed (BRD) by default; whole file refused available.</t>
+          <t>Line-level processing as BRQID.006 asks, with the exceptions listed; partial payments allowed and shown as such. Proposed behaviour: Valid lines are staged and issued; failed lines stay staged with their reason. Available as a setting: Setting of the commission schedule with failed or unmatched lines: valid lines processed (BRD) by default; whole file refused available.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>One OR per insurer / payee and certificate per schedule or batch, as CSHID.007 states. (the system reference FRS: One OR per insurer, certificate and payment for Collection details; one OR per remittance batch (FR-OP-021, OQ49).)</t>
+          <t>One OR per insurer / payee and certificate per schedule or batch, as CSHID.007 states. Proposed behaviour: One OR per insurer, certificate and payment for Collection details; one OR per remittance batch.</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Comptrollership decides the point at which the commission OR is issued; moving it to the Disbursement approval is a change to the system. (the system reference FRS: The commission OR is issued when the Remittance TL approves the batch (FR-OP-035).) Available as a setting: Setting of the point the settlement OR is issued: at the approval of Disbursement (BDOI's reading) by default; at the remittance approval available.</t>
+          <t>Comptrollership decides the point at which the commission OR is issued; moving it to the Disbursement approval is a change to the system. Proposed behaviour: The commission OR is issued when the Remittance TL approves the batch. Available as a setting: Setting of the point the settlement OR is issued: at the approval of Disbursement (BDOI's reading) by default; at the remittance approval available.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Keep Cashiering ownership with requests from Collections, as the BRD-4 Collections FRS specifies; give Marketing read access to the items of its unit. (the system reference FRS: The Cashier assigns and the Cashiering TL approves; Collections asks through Incoming Requests (FR-OP-022; BRD-4).) Available as a setting: Setting of what Marketing users see in the unapplied payment list: their marketing unit (BDOI's reading) by default.</t>
+          <t>Keep Cashiering ownership with requests from Collections, as the BRD-4 Collections FRS specifies; give Marketing read access to the items of its unit. Proposed behaviour: The Cashier assigns and the Cashiering TL approves; Collections asks through Incoming Requests (BRD-4). Available as a setting: Setting of what Marketing users see in the unapplied payment list: their marketing unit (BDOI's reading) by default.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Add AP Unapplied Commission for reversed ORs; keep AR Insurer as a receivable, shown on the list for information. (the system reference FRS: AR Insurer is a receivable from the insurer set up by Adjustment; no AP Unapplied Commission.)</t>
+          <t>Add AP Unapplied Commission for reversed ORs; keep AR Insurer as a receivable, shown on the list for information. Proposed behaviour: AR Insurer is a receivable from the insurer set up by Adjustment; no AP Unapplied Commission.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Keep the the system warehouse (BRD); load it from the PMS list, so PMS stays the source of the checks. (the system reference FRS: Checks are warehoused in the system with a PDCW number and matured by the daily run (FR-OP-016).)</t>
+          <t>Keep the the system warehouse (BRD); load it from the PMS list, so PMS stays the source of the checks. Proposed behaviour: Checks are warehoused in the system with a PDCW number and matured by the daily run.</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's forms. (the system reference FRS: The AR / OR PDF has a Cashier signature line; layout draft (this FRS).)</t>
+          <t>Adopt BDOI's forms. Proposed behaviour: The AR / OR PDF has a Cashier signature line; layout draft (this FRS).</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Set 50 MB. (the system reference FRS: Not stated; the system accepts files up to 25 MB.) Available as a setting: Size limit per payment file type: 50 MB by default.</t>
+          <t>Set 50 MB. Proposed behaviour: Not stated; the system accepts files up to 25 MB. Available as a setting: Size limit per payment file type: 50 MB by default.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>One rate from the Comptrollership table; reversals at the rate of the original receipt. (the system reference FRS: Comptrollership BOOK rate with 2 decimals at the receipt date; cancellation and reinstatement at the receipt's rate (FR-OP-027).)</t>
+          <t>One rate from the Comptrollership table; reversals at the rate of the original receipt. Proposed behaviour: Comptrollership BOOK rate with 2 decimals at the receipt date; cancellation and reinstatement at the receipt's rate.</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Keep the BRD list (it is a maintained list); add the check-payment restriction if BDOI wants it. (the system reference FRS: The BRD lists in four groups, including Check not picked-up, Negative VAT, Discount not applied, PDC retrieval / replacement, Bounced or returned check, Error printing.) Available as a setting: List of the cancellation reasons allowed for a check payment, by default.</t>
+          <t>Keep the BRD list (it is a maintained list); add the check-payment restriction if BDOI wants it. Proposed behaviour: The BRD lists in four groups, including Check not picked-up, Negative VAT, Discount not applied, PDC retrieval / replacement, Bounced or returned check, Error printing. Available as a setting: List of the cancellation reasons allowed for a check payment, by default.</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>By account, with the amount per account shown. (the system reference FRS: Partial reinstatement by amount.)</t>
+          <t>By account, with the amount per account shown. Proposed behaviour: Partial reinstatement by amount.</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Keep them, defaulted from the receipt. (the system reference FRS: Invoice, AR / OR no., assured / payor, amount, Account Officer, Unit Head, Team Leader (premium); not required for a bounced check.)</t>
+          <t>Keep them, defaulted from the receipt. Proposed behaviour: Invoice, AR / OR no., assured / payor, amount, Account Officer, Unit Head, Team Leader (premium); not required for a bounced check.</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enforce it through BDO's network and device policy if required; no change to the screens. (the system reference FRS: Log-in from a browser; responsive screens.) Available as a setting: Setting of the device restriction: off by default for SIT; on with the company networks and the device header of BDOI IT.</t>
+          <t>Enforce it through BDO's network and device policy if required; no change to the screens. Proposed behaviour: Log-in from a browser; responsive screens. Available as a setting: Setting of the device restriction: off by default for SIT; on with the company networks and the device header of BDOI IT.</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Bank account mandatory (defaulted by currency as BDOI proposes); remarks optional. (the system reference FRS: Neither field exists on Receive Payment.) Available as a setting: Setting of the remarks of an AR: mandatory by default.</t>
+          <t>Bank account mandatory (defaulted by currency as BDOI proposes); remarks optional. Proposed behaviour: Neither field exists on Receive Payment. Available as a setting: Setting of the remarks of an AR: mandatory by default.</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Tag per account, defaulted from the client; Comptrollership states the base of the 2% (basic or gross premium); the system keeps the share applied as a parameter. (the system reference FRS: 2% CWT client flag; 98% of the premium applied (FR-OP-018; OQ10).) Available as a setting: Setting of the base of the PR 2307: the premium amount by default; the basic premium available.</t>
+          <t>Tag per account, defaulted from the client; Comptrollership states the base of the 2% (basic or gross premium); the system keeps the share applied as a parameter. Proposed behaviour: 2% CWT client flag; 98% of the premium applied. Available as a setting: Setting of the base of the PR 2307: the premium amount by default; the basic premium available.</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>All applications, with a filter on the source (manual, file, PDC). (the system reference FRS: CSH-APPLIED-PREM lists every applied premium payment.)</t>
+          <t>All applications, with a filter on the source (manual, file, PDC). Proposed behaviour: CSH-APPLIED-PREM lists every applied premium payment.</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Both documents propose the business uploads; record the change against the BRD (CLR-OP-08). (the system reference FRS: The Cashier uploads (FR-OP-015).)</t>
+          <t>Both documents propose the business uploads; record the change against the BRD. Proposed behaviour: The Cashier uploads.</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Specify them in the FRS of Commission Receivables as BDOI maps them, or in the Marketing Collection and Disbursement FRS (BIBS FRS BRD-2 v2.1 FR-OP-113, FR-OP-121); Cashiering keeps the PR 2307 outstanding at payment (FRS.CSH.02.05.13).</t>
+          <t>Specify them in the FRS of Commission Receivables as BDOI maps them, or in the FRS of Marketing Collection and Disbursement; Cashiering keeps the PR 2307 outstanding at payment (FRS.CSH.02.05.13).</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'How to use'!$A$4:$D$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'How to use'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register'!$A$4:$T$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register'!$A$4:$T$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Impact assessment form'!$A$12:$C$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Impact assessment form'!$12:$12</definedName>
@@ -796,7 +796,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-02 Operations Cashiering - after the sign-off of the FRS v3.2</t>
+          <t>BRD-02 Operations Cashiering - after the sign-off of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -939,11 +939,11 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Candidate changes known at v3.2 (status Candidate - for decision) and new requests</t>
+          <t>Candidate changes known at v3.3 (status Candidate - for decision) and new requests</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Row of Appendix R of the FRS v3.2</t>
+          <t>Row of Appendix R of the FRS v3.3</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1948,7 +1948,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Candidate changes known at v3.2 (status Candidate - for decision) and new requests</t>
+          <t>Candidate changes known at v3.3 (status Candidate - for decision) and new requests</t>
         </is>
       </c>
     </row>
@@ -3710,29 +3710,369 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-101</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>iorta TechNXT Project Team</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Appendix J (time rules); FRS.CSH.02.05, FRS.CSH.03.01, FRS.CSH.04.01, FRS.CSH.06.02; FRS Appendix W.2</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Time rules of the Cashiering stages: overdue marker and reminder</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Records waiting for posting or approval are visible on the dashboard but nothing marks them late; a time rule per stage with a marker and a reminder keeps receipts issued the same day.</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: time rules, overdue marker and reminder for the Cashiering stages.</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Within the drop if approved</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>6.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>BDOI to confirm the times (Appendix R, Appendix S)</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>Update the linked test cases</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O24" s="25" t="inlineStr">
+        <is>
+          <t>Candidate - for decision</t>
+        </is>
+      </c>
+      <c r="P24" s="12" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr"/>
+      <c r="R24" s="12" t="inlineStr"/>
+      <c r="S24" s="12" t="inlineStr"/>
+      <c r="T24" s="12" t="inlineStr">
+        <is>
+          <t>TC-OP-002.1-01, TC-OP-002.2-01, TC-OP-002.3-01, TC-OP-010.1-01, TC-OP-010.2-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-102</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>iorta TechNXT Project Team</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>BRQID.006 (extends)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.10.03; Appendix G (failed batch run); FRS Appendix W.2</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>E-mail to a recipient list when a scheduled Cashiering run fails</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>The BRD asks that users are alerted when a run fails; an e-mail to named recipients makes sure a failed overnight run is seen before the business day starts.</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (e-mail to a recipient list).</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>Within the drop if approved</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>2.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>E-mail channel of BDOI</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>Update the linked test cases</t>
+        </is>
+      </c>
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O25" s="25" t="inlineStr">
+        <is>
+          <t>Candidate - for decision</t>
+        </is>
+      </c>
+      <c r="P25" s="12" t="inlineStr"/>
+      <c r="Q25" s="12" t="inlineStr"/>
+      <c r="R25" s="12" t="inlineStr"/>
+      <c r="S25" s="12" t="inlineStr"/>
+      <c r="T25" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-CSH.10.03.01-AC01, TC-FRS-CSH.10.03.01-AC02, TC-OP-008.1-01, TC-OP-008.2-01, TC-OP-008.3-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-103</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>iorta TechNXT Project Team</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>CSHID.023 (extends)</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.01.03.04; FRS Appendix W.2</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Excel export of the Cashiering lists</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Cashiers and Team Leaders work the lists in Excel for reconciliation and follow-up; the BRD asks for extracts of the reports, the FRS extends it to every list.</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (Excel export of the lists).</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Within the drop if approved</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>3 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>Update the linked test cases</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O26" s="25" t="inlineStr">
+        <is>
+          <t>Candidate - for decision</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr"/>
+      <c r="R26" s="12" t="inlineStr"/>
+      <c r="S26" s="12" t="inlineStr"/>
+      <c r="T26" s="12" t="inlineStr">
+        <is>
+          <t>TC-FRS-CSH.01.03.04-AC01, TC-FRS-CSH.01.03.04-AC02, TC-OP-003.4-01, TC-OP-003.1-01, TC-OP-003.2-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>CR-CSH-104</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>iorta TechNXT Project Team</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Appendix G (channel of each notice); FRS Appendix W.2</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Team Leaders who post from branches want the notices also by e-mail; the choice per user and per notice avoids e-mail floods.</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>Within the drop if approved</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>3.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>E-mail channel of BDOI</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr">
+        <is>
+          <t>Test cases to add</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O27" s="25" t="inlineStr">
+        <is>
+          <t>Candidate - for decision</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr"/>
+      <c r="Q27" s="12" t="inlineStr"/>
+      <c r="R27" s="12" t="inlineStr"/>
+      <c r="S27" s="12" t="inlineStr"/>
+      <c r="T27" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:T23"/>
+  <autoFilter ref="A4:T27"/>
   <mergeCells count="1">
     <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O523">
+  <conditionalFormatting sqref="O5:O527">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Closed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:T523">
+  <conditionalFormatting sqref="A5:T527">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H523" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
+    <dataValidation sqref="H5:H527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
       <formula1>'Lists'!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N523" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="N5:N527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O523" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="O5:O527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'How to use'!$A$4:$D$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'How to use'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register'!$A$4:$T$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Register'!$A$4:$T$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Register'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Impact assessment form'!$A$12:$C$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Impact assessment form'!$12:$12</definedName>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1913,7 +1913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3814,22 +3814,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>BRQID.006 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>FRS.CSH.10.03; Appendix G (failed batch run); FRS Appendix W.2</t>
+          <t>Appendix G (channel of each notice); FRS Appendix W.2</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>E-mail to a recipient list when a scheduled Cashiering run fails</t>
+          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>The BRD asks that users are alerted when a run fails; an e-mail to named recipients makes sure a failed overnight run is seen before the business day starts.</t>
+          <t>Team Leaders who post from branches want the notices also by e-mail; the choice per user and per notice avoids e-mail floods.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (e-mail to a recipient list).</t>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>2.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
+          <t>3.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>Update the linked test cases</t>
+          <t>Test cases to add</t>
         </is>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O25" s="25" t="inlineStr">
@@ -3876,203 +3876,31 @@
       <c r="Q25" s="12" t="inlineStr"/>
       <c r="R25" s="12" t="inlineStr"/>
       <c r="S25" s="12" t="inlineStr"/>
-      <c r="T25" s="12" t="inlineStr">
-        <is>
-          <t>TC-FRS-CSH.10.03.01-AC01, TC-FRS-CSH.10.03.01-AC02, TC-OP-008.1-01, TC-OP-008.2-01, TC-OP-008.3-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>CR-CSH-103</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>11-Oct-2026</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>iorta TechNXT Project Team</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>CSHID.023 (extends)</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.03.04; FRS Appendix W.2</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Excel export of the Cashiering lists</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>Cashiers and Team Leaders work the lists in Excel for reconciliation and follow-up; the BRD asks for extracts of the reports, the FRS extends it to every list.</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>Beyond the BRD</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (Excel export of the lists).</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
-        <is>
-          <t>Within the drop if approved</t>
-        </is>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>3 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M26" s="12" t="inlineStr">
-        <is>
-          <t>Update the linked test cases</t>
-        </is>
-      </c>
-      <c r="N26" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O26" s="25" t="inlineStr">
-        <is>
-          <t>Candidate - for decision</t>
-        </is>
-      </c>
-      <c r="P26" s="12" t="inlineStr"/>
-      <c r="Q26" s="12" t="inlineStr"/>
-      <c r="R26" s="12" t="inlineStr"/>
-      <c r="S26" s="12" t="inlineStr"/>
-      <c r="T26" s="12" t="inlineStr">
-        <is>
-          <t>TC-FRS-CSH.01.03.04-AC01, TC-FRS-CSH.01.03.04-AC02, TC-OP-003.4-01, TC-OP-003.1-01, TC-OP-003.2-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>CR-CSH-104</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>11-Oct-2026</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>iorta TechNXT Project Team</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Appendix G (channel of each notice); FRS Appendix W.2</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Team Leaders who post from branches want the notices also by e-mail; the choice per user and per notice avoids e-mail floods.</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>Beyond the BRD</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="inlineStr">
-        <is>
-          <t>Within the drop if approved</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>3.5 md (BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx)</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>E-mail channel of BDOI</t>
-        </is>
-      </c>
-      <c r="M27" s="12" t="inlineStr">
-        <is>
-          <t>Test cases to add</t>
-        </is>
-      </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O27" s="25" t="inlineStr">
-        <is>
-          <t>Candidate - for decision</t>
-        </is>
-      </c>
-      <c r="P27" s="12" t="inlineStr"/>
-      <c r="Q27" s="12" t="inlineStr"/>
-      <c r="R27" s="12" t="inlineStr"/>
-      <c r="S27" s="12" t="inlineStr"/>
-      <c r="T27" s="12" t="inlineStr"/>
+      <c r="T25" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T27"/>
+  <autoFilter ref="A4:T25"/>
   <mergeCells count="1">
     <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O527">
+  <conditionalFormatting sqref="O5:O525">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Closed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:T527">
+  <conditionalFormatting sqref="A5:T525">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
+    <dataValidation sqref="H5:H525" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Choose a value from the list (Type)." type="list">
       <formula1>'Lists'!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="N5:N525" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="O5:O525" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$C$2:$C$9</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -762,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -772,13 +772,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -807,6 +810,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -879,6 +883,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -976,6 +981,7 @@
         <v>83</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -999,6 +1005,8 @@
       </c>
       <c r="C28" s="16" t="inlineStr"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -1058,6 +1066,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -3999,6 +4008,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -4817,7 +4827,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Keep the the system warehouse (BRD); load it from the PMS list, so PMS stays the source of the checks. Proposed behaviour: Checks are warehoused in the system with a PDCW number and matured by the daily run.</t>
+          <t>Keep the system warehouse (BRD); load it from the PMS list, so PMS stays the source of the checks. Proposed behaviour: Checks are warehoused in the system with a PDCW number and matured by the daily run.</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -1026,7 +1026,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1693,7 +1693,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1906,7 +1906,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3917,7 +3917,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4232,7 +4232,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7353,7 +7353,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7516,7 +7516,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Change_Request_Register_v1.0.xlsx
@@ -3915,7 +3915,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Register&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
